--- a/excel-data/restaurant.xlsx
+++ b/excel-data/restaurant.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\mogumogu-pick\excel-data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\MogumoguPick\mogumogu-pick\excel-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6789BA7-6CD3-4AE0-9250-6E55426C6123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2556EE96-84C0-4EE0-98B2-A37770EB7329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2256" yWindow="2592" windowWidth="17280" windowHeight="9648" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
   </bookViews>
   <sheets>
     <sheet name="restaurant" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="255">
   <si>
     <t>restaurant_id</t>
   </si>
@@ -57,24 +58,12 @@
     <t>2025-05-24 12:00:00</t>
   </si>
   <si>
-    <t>鬆餅老師</t>
-  </si>
-  <si>
     <t>https://images.unsplash.com/photo-1669277038512-2dc8b3a2aac8?q=80&amp;w=2048&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.0.3&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
   </si>
   <si>
     <t>2025-05-24 15:06:58</t>
   </si>
   <si>
-    <t>鬆餅厚到可以當枕頭</t>
-  </si>
-  <si>
-    <t>吃飽客</t>
-  </si>
-  <si>
-    <t>披薩大到可以當盾牌</t>
-  </si>
-  <si>
     <t>https://images.unsplash.com/photo-1700323449261-5332ce054718?q=80&amp;w=1931&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
   </si>
   <si>
@@ -84,30 +73,18 @@
     <t>https://images.unsplash.com/photo-1673442635965-34f1b36d8944?q=80&amp;w=2070&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
   </si>
   <si>
-    <t>尊爵有錢人</t>
-  </si>
-  <si>
     <t>https://images.unsplash.com/photo-1565299715199-866c917206bb?q=80&amp;w=1980&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
   </si>
   <si>
     <t>2025-05-24 16:53:58</t>
   </si>
   <si>
-    <t>吃不起但還是吃了</t>
-  </si>
-  <si>
-    <t>牛肉再多點</t>
-  </si>
-  <si>
     <t>https://images.unsplash.com/photo-1631709497146-a239ef373cf1?q=80&amp;w=2070&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
   </si>
   <si>
     <t>2025-06-08 23:49:21</t>
   </si>
   <si>
-    <t>No奶都來</t>
-  </si>
-  <si>
     <t>https://images.unsplash.com/photo-1461023058943-07fcbe16d735?q=80&amp;w=2069&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
   </si>
   <si>
@@ -117,45 +94,24 @@
     <t>2025-06-14 14:51:48</t>
   </si>
   <si>
-    <t>五十籃投手</t>
-  </si>
-  <si>
     <t>https://images.unsplash.com/photo-1525803377221-4f6ccdaa5133?q=80&amp;w=2074&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
   </si>
   <si>
     <t>2025-06-14 15:06:40</t>
   </si>
   <si>
-    <t>喝完好想再投一籃</t>
-  </si>
-  <si>
-    <t>歪堡起司</t>
-  </si>
-  <si>
     <t>https://images.unsplash.com/photo-1610970878459-a0e464d7592b?q=80&amp;w=2124&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
   </si>
   <si>
     <t>2025-06-14 15:03:47</t>
   </si>
   <si>
-    <t>堡堡斜到我都歪了</t>
-  </si>
-  <si>
-    <t>謬奶可可</t>
-  </si>
-  <si>
     <t>https://images.unsplash.com/photo-1563636619-e9143da7973b?q=80&amp;w=1965&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
   </si>
   <si>
     <t>2025-06-14 15:05:47</t>
   </si>
   <si>
-    <t>牛奶濃得像人生誤會</t>
-  </si>
-  <si>
-    <t>真香廚房</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2015/05/02/00/57/aluminous-749358_1280.jpg</t>
   </si>
   <si>
@@ -165,12 +121,6 @@
     <t>2025-06-08 13:40:41</t>
   </si>
   <si>
-    <t>吃完覺得靈魂被淨化了</t>
-  </si>
-  <si>
-    <t>不辣不愛</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2021/06/27/11/00/ma-la-crawfish-6368464_1280.jpg</t>
   </si>
   <si>
@@ -180,12 +130,6 @@
     <t>2024-10-02 21:23:34</t>
   </si>
   <si>
-    <t>我吃過最像家裡煮的外食</t>
-  </si>
-  <si>
-    <t>今天也要吃</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2016/10/30/09/30/hot-chocolate-1782623_1280.jpg</t>
   </si>
   <si>
@@ -195,9 +139,6 @@
     <t>2025-06-17 21:14:21</t>
   </si>
   <si>
-    <t>開動囉食堂</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2020/04/04/15/07/sushi-5002639_1280.jpg</t>
   </si>
   <si>
@@ -207,12 +148,6 @@
     <t>2025-05-18 21:56:09</t>
   </si>
   <si>
-    <t>下次不要再點一樣的</t>
-  </si>
-  <si>
-    <t>再吃會胖屋</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2016/11/08/10/39/chicken-1807883_1280.jpg</t>
   </si>
   <si>
@@ -222,27 +157,18 @@
     <t>2024-12-22 19:53:57</t>
   </si>
   <si>
-    <t>今晚我想來點</t>
-  </si>
-  <si>
     <t>2024-08-30 17:06:01</t>
   </si>
   <si>
     <t>2025-05-24 14:01:15</t>
   </si>
   <si>
-    <t>隨便煮煮</t>
-  </si>
-  <si>
     <t>2025-05-06 15:53:28</t>
   </si>
   <si>
     <t>2025-06-06 19:08:19</t>
   </si>
   <si>
-    <t>問就是牛排</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2018/08/09/07/49/meat-3593929_1280.jpg</t>
   </si>
   <si>
@@ -252,42 +178,21 @@
     <t>2025-06-30 20:23:50</t>
   </si>
   <si>
-    <t>跟照片長得不一樣</t>
-  </si>
-  <si>
-    <t>阿母的味道</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2014/01/09/10/14/kimchi-fried-rice-241051_1280.jpg</t>
   </si>
   <si>
     <t>2025-06-19 15:23:25</t>
   </si>
   <si>
-    <t>打卡專用</t>
-  </si>
-  <si>
-    <t>乾乾拌拌</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2020/03/31/01/56/fried-rice-4985989_1280.jpg</t>
   </si>
   <si>
     <t>2025-01-01 17:39:53</t>
   </si>
   <si>
-    <t>服務態度比飯好</t>
-  </si>
-  <si>
-    <t>湯多一點</t>
-  </si>
-  <si>
     <t>2024-08-22 18:52:38</t>
   </si>
   <si>
-    <t>三分鐘上桌</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2023/05/31/11/14/smoothie-8031132_1280.jpg</t>
   </si>
   <si>
@@ -297,24 +202,12 @@
     <t>2025-07-10 13:22:28</t>
   </si>
   <si>
-    <t>笑死喝個飲料還能打翻</t>
-  </si>
-  <si>
-    <t>醬太多</t>
-  </si>
-  <si>
     <t>2025-03-12 14:58:55</t>
   </si>
   <si>
     <t>2025-05-27 21:02:10</t>
   </si>
   <si>
-    <t>不錯吃，就是太貴</t>
-  </si>
-  <si>
-    <t>外送也排隊</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2022/01/18/19/30/salad-6948004_1280.jpg</t>
   </si>
   <si>
@@ -324,9 +217,6 @@
     <t>2025-06-15 20:32:33</t>
   </si>
   <si>
-    <t>地獄廚神</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2022/05/12/17/05/hamburger-7191898_1280.jpg</t>
   </si>
   <si>
@@ -336,9 +226,6 @@
     <t>2025-07-04 16:28:39</t>
   </si>
   <si>
-    <t>炸你全家</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2019/09/26/18/23/republic-of-korea-4506696_1280.jpg</t>
   </si>
   <si>
@@ -348,42 +235,24 @@
     <t>2024-08-12 20:14:40</t>
   </si>
   <si>
-    <t>四號桌別跑</t>
-  </si>
-  <si>
     <t>2025-03-23 21:42:51</t>
   </si>
   <si>
     <t>2025-04-24 16:31:03</t>
   </si>
   <si>
-    <t>小籠包大冒險</t>
-  </si>
-  <si>
     <t>2025-03-01 14:08:57</t>
   </si>
   <si>
     <t>2025-05-31 15:01:01</t>
   </si>
   <si>
-    <t>店員帥加一星</t>
-  </si>
-  <si>
-    <t>我不挑食</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2016/08/26/21/16/carrot-juice-1623157_960_720.jpg</t>
   </si>
   <si>
     <t>2025-01-16 17:39:31</t>
   </si>
   <si>
-    <t>招牌是健康</t>
-  </si>
-  <si>
-    <t>隱藏口袋店</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2019/08/09/08/14/steak-4394612_1280.jpg</t>
   </si>
   <si>
@@ -399,33 +268,21 @@
     <t>2025-03-05 18:50:37</t>
   </si>
   <si>
-    <t>苦瓜別加</t>
-  </si>
-  <si>
     <t>2025-03-28 13:45:17</t>
   </si>
   <si>
-    <t>咖哩真香</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2015/10/01/14/29/curry-967086_640.jpg</t>
   </si>
   <si>
     <t>2024-10-10 20:24:30</t>
   </si>
   <si>
-    <t>牛奶加點糖</t>
-  </si>
-  <si>
     <t>2024-09-12 15:23:17</t>
   </si>
   <si>
     <t>2025-06-26 15:27:34</t>
   </si>
   <si>
-    <t>甜到蛀牙</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2018/01/26/15/21/hot-3108893_640.jpg</t>
   </si>
   <si>
@@ -435,24 +292,12 @@
     <t>2024-08-09 15:56:33</t>
   </si>
   <si>
-    <t>我喝過最甜的飲料</t>
-  </si>
-  <si>
-    <t>炸雞不香嗎</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2022/05/06/16/17/broasted-chicken-7178658_1280.jpg</t>
   </si>
   <si>
     <t>2024-07-22 17:49:21</t>
   </si>
   <si>
-    <t>笑死吃個飯還能打翻</t>
-  </si>
-  <si>
-    <t>漢堡很圓</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2016/05/25/10/43/hamburger-1414423_1280.jpg</t>
   </si>
   <si>
@@ -462,18 +307,12 @@
     <t>2024-10-20 14:17:39</t>
   </si>
   <si>
-    <t>一杯不到五十</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2022/11/04/00/40/juice-7568712_1280.jpg</t>
   </si>
   <si>
     <t>2024-08-17 18:33:01</t>
   </si>
   <si>
-    <t>續杯會後悔</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2018/03/13/11/39/fruit-3222313_640.jpg</t>
   </si>
   <si>
@@ -483,9 +322,6 @@
     <t>2024-12-18 21:58:12</t>
   </si>
   <si>
-    <t>拌飯拌心情</t>
-  </si>
-  <si>
     <t>https://cdn.pixabay.com/photo/2015/04/10/00/41/food-715542_1280.jpg</t>
   </si>
   <si>
@@ -493,9 +329,6 @@
   </si>
   <si>
     <t>2025-06-25 17:09:48</t>
-  </si>
-  <si>
-    <t>吃完不後悔</t>
   </si>
   <si>
     <t>https://cdn.pixabay.com/photo/2020/02/22/08/55/the-cake-4869920_1280.jpg</t>
@@ -520,72 +353,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>一番湯屋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-07-29 12:07:33</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>這湯的香味可以拿去當香水賣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-07-29 16:41:19</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日式咖哩店</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>飯淋咖哩郎</t>
-  </si>
-  <si>
-    <t>我喝過最像樣的飲料</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>飯丸本舖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>傳說中吃太快會跟飯丸變朋友的那間店</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-07-29 17:06:19</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>麵有引力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主打「你不靠近，我麵也會拉你過來。」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-07-29 17:05:31</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奶味很濃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>牛肉比麵還多，驚訝！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鹽味本舖</t>
-  </si>
-  <si>
-    <t>老闆只信三樣東西，鹽、柴魚和他的直覺</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>group_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -594,10 +361,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1590947132387-155cc02f3212?q=80&amp;w=2070&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.0.3&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>餐廳分類 ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -640,6 +403,413 @@
   <si>
     <t>群組內排序 ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>address</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雙月食品社 青島店</t>
+  </si>
+  <si>
+    <t>台北市中正區青島東路6之2號</t>
+  </si>
+  <si>
+    <t>雞湯很讚，天冷會想再來</t>
+  </si>
+  <si>
+    <t>2025-07-29 12:07:33</t>
+  </si>
+  <si>
+    <t>武田咖哩</t>
+  </si>
+  <si>
+    <t>台北市松山區三民路146號</t>
+  </si>
+  <si>
+    <t>2025-07-29 16:41:19</t>
+  </si>
+  <si>
+    <t>小木屋鬆餅 台北圓山店</t>
+  </si>
+  <si>
+    <t>台北市大同區酒泉街30之1號1樓</t>
+  </si>
+  <si>
+    <t>蘇阿姨比薩屋</t>
+  </si>
+  <si>
+    <t>台北市大安區光復南路300號</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1590947132387-155cc02f3212?q=80&amp;w=2070&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.0.3&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+  </si>
+  <si>
+    <t>軟食力</t>
+  </si>
+  <si>
+    <t>台北市中山區民權東路二段135巷30弄21號</t>
+  </si>
+  <si>
+    <t>2025-07-29 17:06:19</t>
+  </si>
+  <si>
+    <t>賣麵炎仔</t>
+  </si>
+  <si>
+    <t>台北市大同區安西街106號</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>2025-07-29 17:05:31</t>
+  </si>
+  <si>
+    <t>Butcher by LanPengYou</t>
+  </si>
+  <si>
+    <t>台北市大安區和平東路二段118巷4-1號1樓</t>
+  </si>
+  <si>
+    <t>老山東牛肉家常麵店</t>
+  </si>
+  <si>
+    <t>台北市萬華區西寧南路70號B1之15室</t>
+  </si>
+  <si>
+    <t>麵很Q，牛肉給得算大方</t>
+  </si>
+  <si>
+    <t>Fika Fika Cafe 伊通門市</t>
+  </si>
+  <si>
+    <t>台北市中山區伊通街33號</t>
+  </si>
+  <si>
+    <t>50嵐 西門店</t>
+  </si>
+  <si>
+    <t>台北市萬華區漢中街136號</t>
+  </si>
+  <si>
+    <t>Burger Ray 忠孝店</t>
+  </si>
+  <si>
+    <t>台北市大安區忠孝東路四段250-4號</t>
+  </si>
+  <si>
+    <t>迷客夏 台北農安店</t>
+  </si>
+  <si>
+    <t>台北市中山區農安街12號</t>
+  </si>
+  <si>
+    <t>黃記魯肉飯</t>
+  </si>
+  <si>
+    <t>台北市中山區中山北路二段183巷28號</t>
+  </si>
+  <si>
+    <t>祥和蔬食 中正店</t>
+  </si>
+  <si>
+    <t>台北市中正區鎮江街1巷1號</t>
+  </si>
+  <si>
+    <t>辣度比想像中高，下次點小辣</t>
+  </si>
+  <si>
+    <t>HUGH dessert dining</t>
+  </si>
+  <si>
+    <t>台北市大同區重慶北路三段136巷56號</t>
+  </si>
+  <si>
+    <t>三味食堂</t>
+  </si>
+  <si>
+    <t>台北市萬華區貴陽街二段116號</t>
+  </si>
+  <si>
+    <t>炸雞大獅 北市公館店</t>
+  </si>
+  <si>
+    <t>台北市中正區羅斯福路四段24巷14號</t>
+  </si>
+  <si>
+    <t>一甲子餐飲</t>
+  </si>
+  <si>
+    <t>台北市萬華區康定路79號</t>
+  </si>
+  <si>
+    <t>鍾家原上海生煎包</t>
+  </si>
+  <si>
+    <t>台北市士林區小東街38號</t>
+  </si>
+  <si>
+    <t>A CUT 牛排館</t>
+  </si>
+  <si>
+    <t>台北市中山區遼寧街177號2樓</t>
+  </si>
+  <si>
+    <t>牛排不錯，但假日人很多</t>
+  </si>
+  <si>
+    <t>娘子韓食 市民店</t>
+  </si>
+  <si>
+    <t>台北市松山區市民大道四段173號</t>
+  </si>
+  <si>
+    <t>民生炒飯專賣店</t>
+  </si>
+  <si>
+    <t>台北市松山區民生東路五段27號</t>
+  </si>
+  <si>
+    <t>吾旺再季</t>
+  </si>
+  <si>
+    <t>台北市中正區中華路二段313巷29號</t>
+  </si>
+  <si>
+    <t>麻古茶坊 台北公館店</t>
+  </si>
+  <si>
+    <t>台北市中正區羅斯福路三段316巷5號</t>
+  </si>
+  <si>
+    <t>源芳刈包</t>
+  </si>
+  <si>
+    <t>台北市萬華區華西街17之2號</t>
+  </si>
+  <si>
+    <t>小小樹食 大安店</t>
+  </si>
+  <si>
+    <t>台北市大安區大安路一段116巷17號</t>
+  </si>
+  <si>
+    <t>Pàng 胖塔可</t>
+  </si>
+  <si>
+    <t>台北市大安區文昌街181號1樓</t>
+  </si>
+  <si>
+    <t>有有1969</t>
+  </si>
+  <si>
+    <t>台北市中山區遼寧街48號</t>
+  </si>
+  <si>
+    <t>大橋頭老牌筒仔米糕</t>
+  </si>
+  <si>
+    <t>台北市大同區延平北路三段41號</t>
+  </si>
+  <si>
+    <t>杭州小籠湯包 創始店</t>
+  </si>
+  <si>
+    <t>台北市大安區杭州南路二段19號</t>
+  </si>
+  <si>
+    <t>小籠包要趁熱吃，冷掉差很多</t>
+  </si>
+  <si>
+    <t>Little Tree Juice Club</t>
+  </si>
+  <si>
+    <t>台北市大安區忠孝東路三段268號4樓</t>
+  </si>
+  <si>
+    <t>藍家牛排館</t>
+  </si>
+  <si>
+    <t>台北市松山區富錦街26號</t>
+  </si>
+  <si>
+    <t>誠記越南麵食館 永康總店</t>
+  </si>
+  <si>
+    <t>台北市大安區永康街6巷1號</t>
+  </si>
+  <si>
+    <t>雄記蔥抓餅</t>
+  </si>
+  <si>
+    <t>台北市中正區羅斯福路四段108巷2號</t>
+  </si>
+  <si>
+    <t>番紅花印度美饌</t>
+  </si>
+  <si>
+    <t>台北市士林區天母東路38之6號</t>
+  </si>
+  <si>
+    <t>得正 台北雙連計劃</t>
+  </si>
+  <si>
+    <t>台北市大同區民生西路122號</t>
+  </si>
+  <si>
+    <t>COMEBUY 台北古亭店</t>
+  </si>
+  <si>
+    <t>台北市中正區羅斯福路二段58號</t>
+  </si>
+  <si>
+    <t>師園鹽酥雞 師大店</t>
+  </si>
+  <si>
+    <t>台北市大安區師大路39巷14號</t>
+  </si>
+  <si>
+    <t>Furger 芙格漢堡 公館店</t>
+  </si>
+  <si>
+    <t>台北市中正區羅斯福路四段52巷2號</t>
+  </si>
+  <si>
+    <t>可不可熟成紅茶 台北站前店</t>
+  </si>
+  <si>
+    <t>台北市中正區南陽街34號</t>
+  </si>
+  <si>
+    <t>龜記茗品 公館店</t>
+  </si>
+  <si>
+    <t>台北市中正區汀州路三段174-1號</t>
+  </si>
+  <si>
+    <t>開囍</t>
+  </si>
+  <si>
+    <t>台北市信義區莊敬路441號</t>
+  </si>
+  <si>
+    <t>紅葉蛋糕 仁愛總店</t>
+  </si>
+  <si>
+    <t>台北市大安區仁愛路三段26-5號</t>
+  </si>
+  <si>
+    <t>蛋糕不會太甜，生日可以再買</t>
+  </si>
+  <si>
+    <t>2025-05-22 15:36:50</t>
+  </si>
+  <si>
+    <t>2025-05-08 8:58:00</t>
+  </si>
+  <si>
+    <t>2025-05-24 15:14:58</t>
+  </si>
+  <si>
+    <t>2025-05-24 12:09:00</t>
+  </si>
+  <si>
+    <t>2024-11-09 14:51:19</t>
+  </si>
+  <si>
+    <t>2025-03-16 13:58:49</t>
+  </si>
+  <si>
+    <t>2024-07-18 17:01:20</t>
+  </si>
+  <si>
+    <t>2024-07-22 17:19:01</t>
+  </si>
+  <si>
+    <t>2025-04-17 16:05:33</t>
+  </si>
+  <si>
+    <t>2024-06-09 11:09:49</t>
+  </si>
+  <si>
+    <t>2024-11-01 15:47:11</t>
+  </si>
+  <si>
+    <t>2024-07-29 13:48:01</t>
+  </si>
+  <si>
+    <t>2025-04-03 11:34:28</t>
+  </si>
+  <si>
+    <t>2025-05-20 12:25:56</t>
+  </si>
+  <si>
+    <t>2025-05-29 13:02:25</t>
+  </si>
+  <si>
+    <t>2025-06-19 15:29:25</t>
+  </si>
+  <si>
+    <t>2025-01-15 13:49:56</t>
+  </si>
+  <si>
+    <t>2025-02-13 12:33:55</t>
+  </si>
+  <si>
+    <t>2025-03-23 10:54:59</t>
+  </si>
+  <si>
+    <t>2025-05-12 9:41:44</t>
+  </si>
+  <si>
+    <t>2024-06-19 18:06:47</t>
+  </si>
+  <si>
+    <t>2025-02-20 18:13:51</t>
+  </si>
+  <si>
+    <t>2025-02-01 10:38:57</t>
+  </si>
+  <si>
+    <t>2024-12-16 14:08:31</t>
+  </si>
+  <si>
+    <t>2025-01-16 17:55:31</t>
+  </si>
+  <si>
+    <t>2025-05-07 11:37:28</t>
+  </si>
+  <si>
+    <t>2025-05-30 14:26:28</t>
+  </si>
+  <si>
+    <t>2025-01-22 9:35:24</t>
+  </si>
+  <si>
+    <t>2024-08-04 11:47:17</t>
+  </si>
+  <si>
+    <t>2024-06-19 12:32:25</t>
+  </si>
+  <si>
+    <t>2024-05-24 15:55:16</t>
+  </si>
+  <si>
+    <t>2024-10-16 16:52:17</t>
+  </si>
+  <si>
+    <t>2024-08-22 17:27:25</t>
+  </si>
+  <si>
+    <t>2025-04-06 13:02:33</t>
+  </si>
+  <si>
+    <t>2025-05-20 17:13:33</t>
   </si>
 </sst>
 </file>
@@ -1073,85 +1243,91 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E49155C-24E6-44A5-B674-54852AEBDB71}">
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="22.77734375" style="1" customWidth="1"/>
-    <col min="6" max="8" width="22.77734375" customWidth="1"/>
-    <col min="9" max="11" width="22.77734375" style="1" customWidth="1"/>
+    <col min="6" max="9" width="22.77734375" customWidth="1"/>
+    <col min="10" max="12" width="22.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>159</v>
+        <v>103</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>183</v>
+        <v>109</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>186</v>
+        <v>112</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>160</v>
+        <v>104</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>187</v>
+        <v>105</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>180</v>
+        <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>192</v>
+        <v>118</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>185</v>
+        <v>111</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1168,25 +1344,28 @@
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="G3" t="s">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="H3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>164</v>
-      </c>
       <c r="K3" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1203,25 +1382,25 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="G4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I4" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>166</v>
-      </c>
       <c r="K4" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1238,25 +1417,25 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" t="s">
+        <v>130</v>
+      </c>
+      <c r="I5" t="s">
         <v>10</v>
       </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="J5" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L5" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1273,25 +1452,25 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>182</v>
-      </c>
-      <c r="I6" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L6" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1308,25 +1487,25 @@
         <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="G7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>17</v>
+        <v>135</v>
+      </c>
+      <c r="I7" t="s">
+        <v>12</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1343,23 +1522,25 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="G8" t="s">
-        <v>174</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="4"/>
+        <v>138</v>
+      </c>
+      <c r="I8" t="s">
+        <v>14</v>
+      </c>
       <c r="J8" s="4" t="s">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1376,23 +1557,25 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="4"/>
+        <v>142</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
       <c r="J9" s="4" t="s">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1409,23 +1592,28 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="G10" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="4"/>
+        <v>145</v>
+      </c>
+      <c r="I10" t="s">
+        <v>17</v>
+      </c>
       <c r="J10" s="4" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1442,25 +1630,25 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>146</v>
       </c>
       <c r="G11" t="s">
-        <v>176</v>
-      </c>
-      <c r="H11" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>28</v>
+        <v>147</v>
+      </c>
+      <c r="I11" t="s">
+        <v>19</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1477,23 +1665,25 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>148</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="4"/>
+        <v>149</v>
+      </c>
+      <c r="I12" t="s">
+        <v>22</v>
+      </c>
       <c r="J12" s="4" t="s">
-        <v>32</v>
+        <v>139</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1510,23 +1700,25 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>34</v>
+        <v>150</v>
       </c>
       <c r="G13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" s="4"/>
+        <v>151</v>
+      </c>
+      <c r="I13" t="s">
+        <v>24</v>
+      </c>
       <c r="J13" s="4" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1543,23 +1735,25 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>38</v>
+        <v>152</v>
       </c>
       <c r="G14" t="s">
-        <v>41</v>
-      </c>
-      <c r="H14" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="4"/>
+        <v>153</v>
+      </c>
+      <c r="I14" t="s">
+        <v>26</v>
+      </c>
       <c r="J14" s="4" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1576,25 +1770,25 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>44</v>
+        <v>155</v>
+      </c>
+      <c r="I15" t="s">
+        <v>28</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1611,25 +1805,28 @@
         <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>47</v>
+        <v>156</v>
       </c>
       <c r="G16" t="s">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>49</v>
+        <v>158</v>
+      </c>
+      <c r="I16" t="s">
+        <v>31</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1646,25 +1843,25 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>159</v>
       </c>
       <c r="G17" t="s">
-        <v>46</v>
-      </c>
-      <c r="H17" t="s">
-        <v>53</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>54</v>
+        <v>160</v>
+      </c>
+      <c r="I17" t="s">
+        <v>34</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1681,25 +1878,25 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="G18" t="s">
-        <v>60</v>
-      </c>
-      <c r="H18" t="s">
-        <v>57</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>58</v>
+        <v>162</v>
+      </c>
+      <c r="I18" t="s">
+        <v>37</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>229</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1716,25 +1913,25 @@
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>163</v>
       </c>
       <c r="G19" t="s">
-        <v>51</v>
-      </c>
-      <c r="H19" t="s">
-        <v>62</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>63</v>
+        <v>164</v>
+      </c>
+      <c r="I19" t="s">
+        <v>40</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1751,22 +1948,25 @@
         <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>165</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>66</v>
+        <v>166</v>
+      </c>
+      <c r="I20" t="s">
+        <v>139</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1783,22 +1983,25 @@
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>68</v>
+        <v>167</v>
       </c>
       <c r="G21" t="s">
+        <v>168</v>
+      </c>
+      <c r="I21" t="s">
+        <v>139</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1815,25 +2018,28 @@
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="G22" t="s">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="H22" t="s">
-        <v>72</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>73</v>
+        <v>171</v>
+      </c>
+      <c r="I22" t="s">
+        <v>47</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1850,25 +2056,25 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>76</v>
+        <v>172</v>
       </c>
       <c r="G23" t="s">
-        <v>79</v>
-      </c>
-      <c r="H23" t="s">
-        <v>77</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>78</v>
+        <v>173</v>
+      </c>
+      <c r="I23" t="s">
+        <v>50</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1885,23 +2091,25 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="G24" t="s">
-        <v>83</v>
-      </c>
-      <c r="H24" t="s">
-        <v>81</v>
-      </c>
-      <c r="I24" s="4"/>
+        <v>175</v>
+      </c>
+      <c r="I24" t="s">
+        <v>52</v>
+      </c>
       <c r="J24" s="4" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1918,20 +2126,25 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="G25" t="s">
-        <v>79</v>
-      </c>
-      <c r="I25" s="4"/>
+        <v>177</v>
+      </c>
+      <c r="I25" t="s">
+        <v>139</v>
+      </c>
       <c r="J25" s="4" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1948,25 +2161,25 @@
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="G26" t="s">
-        <v>90</v>
-      </c>
-      <c r="H26" t="s">
-        <v>87</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>88</v>
+        <v>179</v>
+      </c>
+      <c r="I26" t="s">
+        <v>55</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>236</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1983,22 +2196,25 @@
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="G27" t="s">
-        <v>94</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>92</v>
+        <v>181</v>
+      </c>
+      <c r="I27" t="s">
+        <v>139</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>237</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -2015,25 +2231,25 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="G28" t="s">
-        <v>51</v>
-      </c>
-      <c r="H28" t="s">
-        <v>96</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>97</v>
+        <v>183</v>
+      </c>
+      <c r="I28" t="s">
+        <v>60</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>238</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -2050,25 +2266,25 @@
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>99</v>
+        <v>184</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
-      </c>
-      <c r="H29" t="s">
-        <v>100</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>101</v>
+        <v>185</v>
+      </c>
+      <c r="I29" t="s">
+        <v>63</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>239</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -2085,25 +2301,25 @@
         <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="G30" t="s">
-        <v>83</v>
-      </c>
-      <c r="H30" t="s">
-        <v>104</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>105</v>
+        <v>187</v>
+      </c>
+      <c r="I30" t="s">
+        <v>66</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -2120,22 +2336,25 @@
         <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>107</v>
+        <v>188</v>
       </c>
       <c r="G31" t="s">
-        <v>51</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>108</v>
+        <v>189</v>
+      </c>
+      <c r="I31" t="s">
+        <v>139</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>241</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -2152,22 +2371,28 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="G32" t="s">
-        <v>113</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>111</v>
+        <v>191</v>
+      </c>
+      <c r="H32" t="s">
+        <v>192</v>
+      </c>
+      <c r="I32" t="s">
+        <v>139</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>242</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -2184,25 +2409,25 @@
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="G33" t="s">
-        <v>117</v>
-      </c>
-      <c r="H33" t="s">
-        <v>115</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>116</v>
+        <v>194</v>
+      </c>
+      <c r="I33" t="s">
+        <v>73</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>243</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -2219,25 +2444,25 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="G34" t="s">
-        <v>83</v>
-      </c>
-      <c r="H34" t="s">
-        <v>119</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>120</v>
+        <v>196</v>
+      </c>
+      <c r="I34" t="s">
+        <v>75</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -2254,25 +2479,25 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="G35" t="s">
-        <v>179</v>
-      </c>
-      <c r="H35" t="s">
-        <v>121</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>122</v>
+        <v>198</v>
+      </c>
+      <c r="I35" t="s">
+        <v>77</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>247</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -2289,20 +2514,25 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>124</v>
+        <v>199</v>
       </c>
       <c r="G36" t="s">
-        <v>60</v>
-      </c>
-      <c r="I36" s="4"/>
+        <v>200</v>
+      </c>
+      <c r="I36" t="s">
+        <v>139</v>
+      </c>
       <c r="J36" s="4" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -2319,23 +2549,25 @@
         <v>0</v>
       </c>
       <c r="F37" t="s">
-        <v>126</v>
+        <v>201</v>
       </c>
       <c r="G37" t="s">
-        <v>60</v>
-      </c>
-      <c r="H37" t="s">
-        <v>127</v>
-      </c>
-      <c r="I37" s="4"/>
+        <v>202</v>
+      </c>
+      <c r="I37" t="s">
+        <v>81</v>
+      </c>
       <c r="J37" s="4" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -2352,22 +2584,25 @@
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="G38" t="s">
-        <v>79</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>130</v>
+        <v>204</v>
+      </c>
+      <c r="I38" t="s">
+        <v>139</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -2384,25 +2619,25 @@
         <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>132</v>
+        <v>205</v>
       </c>
       <c r="G39" t="s">
-        <v>136</v>
-      </c>
-      <c r="H39" t="s">
-        <v>133</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>134</v>
+        <v>206</v>
+      </c>
+      <c r="I39" t="s">
+        <v>85</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -2419,23 +2654,25 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="G40" t="s">
-        <v>140</v>
-      </c>
-      <c r="H40" t="s">
-        <v>138</v>
-      </c>
-      <c r="I40" s="4"/>
+        <v>208</v>
+      </c>
+      <c r="I40" t="s">
+        <v>88</v>
+      </c>
       <c r="J40" s="4" t="s">
         <v>139</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -2452,25 +2689,25 @@
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="G41" t="s">
-        <v>83</v>
-      </c>
-      <c r="H41" t="s">
-        <v>142</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>143</v>
+        <v>210</v>
+      </c>
+      <c r="I41" t="s">
+        <v>90</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -2487,23 +2724,25 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>145</v>
+        <v>211</v>
       </c>
       <c r="G42" t="s">
-        <v>169</v>
-      </c>
-      <c r="H42" t="s">
-        <v>146</v>
-      </c>
-      <c r="I42" s="4"/>
+        <v>212</v>
+      </c>
+      <c r="I42" t="s">
+        <v>93</v>
+      </c>
       <c r="J42" s="4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -2520,25 +2759,25 @@
         <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>148</v>
+        <v>213</v>
       </c>
       <c r="G43" t="s">
-        <v>75</v>
-      </c>
-      <c r="H43" t="s">
-        <v>149</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>150</v>
+        <v>214</v>
+      </c>
+      <c r="I43" t="s">
+        <v>95</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>151</v>
+        <v>96</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -2555,25 +2794,25 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="G44" t="s">
-        <v>94</v>
-      </c>
-      <c r="H44" t="s">
-        <v>153</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>154</v>
+        <v>216</v>
+      </c>
+      <c r="I44" t="s">
+        <v>98</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -2590,25 +2829,39 @@
         <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>156</v>
+        <v>217</v>
       </c>
       <c r="G45" t="s">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="H45" t="s">
-        <v>157</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>158</v>
+        <v>219</v>
+      </c>
+      <c r="I45" t="s">
+        <v>101</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>158</v>
+        <v>253</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E214872-B259-4D60-A09C-B4FCA0969047}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel-data/restaurant.xlsx
+++ b/excel-data/restaurant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\MogumoguPick\mogumogu-pick\excel-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2556EE96-84C0-4EE0-98B2-A37770EB7329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B511073C-2512-41F6-8378-FE9F3B7DFEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="260">
   <si>
     <t>restaurant_id</t>
   </si>
@@ -70,9 +70,6 @@
     <t>2024-11-28 15:56:19</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1673442635965-34f1b36d8944?q=80&amp;w=2070&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
-  </si>
-  <si>
     <t>https://images.unsplash.com/photo-1565299715199-866c917206bb?q=80&amp;w=1980&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
   </si>
   <si>
@@ -112,18 +109,12 @@
     <t>2025-06-14 15:05:47</t>
   </si>
   <si>
-    <t>https://cdn.pixabay.com/photo/2015/05/02/00/57/aluminous-749358_1280.jpg</t>
-  </si>
-  <si>
     <t>2024-08-14 20:14:20</t>
   </si>
   <si>
     <t>2025-06-08 13:40:41</t>
   </si>
   <si>
-    <t>https://cdn.pixabay.com/photo/2021/06/27/11/00/ma-la-crawfish-6368464_1280.jpg</t>
-  </si>
-  <si>
     <t>2024-08-19 21:33:01</t>
   </si>
   <si>
@@ -169,9 +160,6 @@
     <t>2025-06-06 19:08:19</t>
   </si>
   <si>
-    <t>https://cdn.pixabay.com/photo/2018/08/09/07/49/meat-3593929_1280.jpg</t>
-  </si>
-  <si>
     <t>2025-06-27 15:45:56</t>
   </si>
   <si>
@@ -217,18 +205,12 @@
     <t>2025-06-15 20:32:33</t>
   </si>
   <si>
-    <t>https://cdn.pixabay.com/photo/2022/05/12/17/05/hamburger-7191898_1280.jpg</t>
-  </si>
-  <si>
     <t>2025-06-11 13:08:44</t>
   </si>
   <si>
     <t>2025-07-04 16:28:39</t>
   </si>
   <si>
-    <t>https://cdn.pixabay.com/photo/2019/09/26/18/23/republic-of-korea-4506696_1280.jpg</t>
-  </si>
-  <si>
     <t>2024-07-20 21:34:47</t>
   </si>
   <si>
@@ -283,9 +265,6 @@
     <t>2025-06-26 15:27:34</t>
   </si>
   <si>
-    <t>https://cdn.pixabay.com/photo/2018/01/26/15/21/hot-3108893_640.jpg</t>
-  </si>
-  <si>
     <t>2024-07-29 16:09:25</t>
   </si>
   <si>
@@ -307,9 +286,6 @@
     <t>2024-10-20 14:17:39</t>
   </si>
   <si>
-    <t>https://cdn.pixabay.com/photo/2022/11/04/00/40/juice-7568712_1280.jpg</t>
-  </si>
-  <si>
     <t>2024-08-17 18:33:01</t>
   </si>
   <si>
@@ -322,16 +298,10 @@
     <t>2024-12-18 21:58:12</t>
   </si>
   <si>
-    <t>https://cdn.pixabay.com/photo/2015/04/10/00/41/food-715542_1280.jpg</t>
-  </si>
-  <si>
     <t>2024-10-04 21:09:25</t>
   </si>
   <si>
     <t>2025-06-25 17:09:48</t>
-  </si>
-  <si>
-    <t>https://cdn.pixabay.com/photo/2020/02/22/08/55/the-cake-4869920_1280.jpg</t>
   </si>
   <si>
     <t>2025-05-20 16:45:33</t>
@@ -810,13 +780,61 @@
   </si>
   <si>
     <t>2025-05-20 17:13:33</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1682496178083-74db4a32e473?auto=format&amp;fit=crop&amp;fm=jpg&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D&amp;ixlib=rb-4.1.0&amp;q=60&amp;w=3000</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1769065647078-f067eb768035?auto=format&amp;fit=crop&amp;fm=jpg&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D&amp;ixlib=rb-4.1.0&amp;q=60&amp;w=3000</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1781785164696-0154e4dd70c1?auto=format&amp;fit=crop&amp;fm=jpg&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D&amp;ixlib=rb-4.1.0&amp;q=60&amp;w=3000</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1768326119773-05cae29f4106?auto=format&amp;fit=crop&amp;fm=jpg&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D&amp;ixlib=rb-4.1.0&amp;q=60&amp;w=3000</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1761315413828-0a63516507ff?auto=format&amp;fit=crop&amp;fm=jpg&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D&amp;ixlib=rb-4.1.0&amp;q=60&amp;w=3000</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1561881660-c0fac77e431e?auto=format&amp;fit=crop&amp;fm=jpg&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D&amp;ixlib=rb-4.1.0&amp;q=60&amp;w=3000</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1766758196906-0df069a802af?auto=format&amp;fit=crop&amp;fm=jpg&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D&amp;ixlib=rb-4.1.0&amp;q=60&amp;w=3000</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1669251034889-33e3036a531d?auto=format&amp;fit=crop&amp;fm=jpg&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D&amp;ixlib=rb-4.1.0&amp;q=60&amp;w=3000</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1762418967889-10abec43c325?auto=format&amp;fit=crop&amp;fm=jpg&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D&amp;ixlib=rb-4.1.0&amp;q=60&amp;w=3000</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1759302307381-bdccf7b35e5d?auto=format&amp;fit=crop&amp;fm=jpg&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D&amp;ixlib=rb-4.1.0&amp;q=60&amp;w=3000</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1774979300628-12e379acea7b?auto=format&amp;fit=crop&amp;fm=jpg&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D&amp;ixlib=rb-4.1.0&amp;q=60&amp;w=3000</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1741241858511-13978ec7a067?auto=format&amp;fit=crop&amp;fm=jpg&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D&amp;ixlib=rb-4.1.0&amp;q=60&amp;w=3000</t>
+  </si>
+  <si>
+    <t>https://images.unsplash.com/photo-1673442635965-34f1b36d8944?q=80&amp;w=2070&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxwaG90by1wYWdlfHx8fGVufDB8fHx8fA%3D%3D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://cdn.pixabay.com/photo/2018/08/09/07/49/meat-3593929_1280.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://cdn.pixabay.com/photo/2015/08/31/23/42/cake-916253_1280.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -827,6 +845,19 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -888,12 +919,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -909,9 +945,18 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="Normal" xfId="2" xr:uid="{22E097CA-FC8A-4223-A8A8-9EAE94ECA6EE}"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="一般 2" xfId="1" xr:uid="{258F5156-DBF9-4434-9711-07FE4561C448}"/>
+    <cellStyle name="超連結" xfId="3" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1244,72 +1289,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E49155C-24E6-44A5-B674-54852AEBDB71}">
   <dimension ref="A1:L45"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="5" width="22.77734375" style="1" customWidth="1"/>
     <col min="6" max="9" width="22.77734375" customWidth="1"/>
     <col min="10" max="12" width="22.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="K1" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>4</v>
@@ -1321,13 +1366,13 @@
         <v>3</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="25.05" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1344,13 +1389,13 @@
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G3" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="I3" t="s">
         <v>5</v>
@@ -1359,13 +1404,13 @@
         <v>6</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="25.05" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1382,10 +1427,10 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="G4" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I4" t="s">
         <v>8</v>
@@ -1394,13 +1439,13 @@
         <v>9</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="25.05" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1417,10 +1462,10 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="G5" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="I5" t="s">
         <v>10</v>
@@ -1432,10 +1477,10 @@
         <v>7</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="25.05" customHeight="1">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1452,13 +1497,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="G6" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="I6" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>9</v>
@@ -1467,10 +1512,10 @@
         <v>7</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="25.05" customHeight="1">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1487,10 +1532,10 @@
         <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="G7" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="I7" t="s">
         <v>12</v>
@@ -1499,13 +1544,13 @@
         <v>13</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="25.05" customHeight="1">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1522,25 +1567,25 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="G8" t="s">
-        <v>138</v>
-      </c>
-      <c r="I8" t="s">
-        <v>14</v>
+        <v>128</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>257</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="25.05" customHeight="1">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1557,25 +1602,25 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="G9" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="I9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="L9" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="25.05" customHeight="1">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1592,28 +1637,28 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="G10" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H10" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="I10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="L10" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="25.05" customHeight="1">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1630,25 +1675,25 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="G11" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="K11" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="L11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:12" ht="25.05" customHeight="1">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1665,25 +1710,25 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="G12" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="L12" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="25.05" customHeight="1">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1700,25 +1745,25 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G13" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="I13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="L13" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="25.05" customHeight="1">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1735,25 +1780,25 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="G14" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="I14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="L14" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="25.05" customHeight="1">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1770,25 +1815,25 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="G15" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="I15" t="s">
+        <v>245</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:12" ht="25.05" customHeight="1">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1805,28 +1850,28 @@
         <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="G16" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="H16" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>246</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="25.05" customHeight="1">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1843,25 +1888,25 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="G17" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="I17" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="25.05" customHeight="1">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1878,25 +1923,25 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="G18" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="I18" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="25.05" customHeight="1">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1913,25 +1958,25 @@
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="G19" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="25.05" customHeight="1">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1948,25 +1993,25 @@
         <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="G20" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="I20" t="s">
-        <v>139</v>
+        <v>247</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="25.05" customHeight="1">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1983,25 +2028,25 @@
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="G21" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="I21" t="s">
-        <v>139</v>
+        <v>248</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="25.05" customHeight="1">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -2018,28 +2063,28 @@
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="G22" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="H22" t="s">
-        <v>171</v>
-      </c>
-      <c r="I22" t="s">
-        <v>47</v>
+        <v>161</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>258</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="25.05" customHeight="1">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -2056,25 +2101,25 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="G23" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="I23" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="25.05" customHeight="1">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -2091,25 +2136,25 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="G24" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="I24" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="25.05" customHeight="1">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -2126,25 +2171,25 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="G25" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="I25" t="s">
-        <v>139</v>
+        <v>249</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="25.05" customHeight="1">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -2161,25 +2206,25 @@
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="G26" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I26" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="25.05" customHeight="1">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -2196,25 +2241,25 @@
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G27" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="I27" t="s">
-        <v>139</v>
+        <v>247</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="25.05" customHeight="1">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -2231,25 +2276,25 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="G28" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="I28" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="25.05" customHeight="1">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -2266,25 +2311,25 @@
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="G29" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="I29" t="s">
-        <v>63</v>
+        <v>250</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="25.05" customHeight="1">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -2301,25 +2346,25 @@
         <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="G30" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="I30" t="s">
-        <v>66</v>
+        <v>251</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="25.05" customHeight="1">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -2336,25 +2381,25 @@
         <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="G31" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="I31" t="s">
-        <v>139</v>
+        <v>252</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="25.05" customHeight="1">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -2371,28 +2416,28 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="G32" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="H32" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="I32" t="s">
-        <v>139</v>
+        <v>253</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="25.05" customHeight="1">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -2409,25 +2454,25 @@
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="G33" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="I33" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="25.05" customHeight="1">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -2444,25 +2489,25 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="G34" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="I34" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="25.05" customHeight="1">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -2479,25 +2524,25 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="G35" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="I35" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="25.05" customHeight="1">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -2514,25 +2559,25 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="G36" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="I36" t="s">
-        <v>139</v>
+        <v>254</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="25.05" customHeight="1">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -2549,25 +2594,25 @@
         <v>0</v>
       </c>
       <c r="F37" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G37" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="I37" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="25.05" customHeight="1">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -2584,25 +2629,25 @@
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="G38" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="I38" t="s">
-        <v>139</v>
+        <v>255</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="25.05" customHeight="1">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -2619,25 +2664,25 @@
         <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="G39" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="I39" t="s">
-        <v>85</v>
+        <v>255</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="25.05" customHeight="1">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -2654,25 +2699,25 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="G40" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="I40" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="25.05" customHeight="1">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -2689,25 +2734,25 @@
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="G41" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="I41" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="25.05" customHeight="1">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -2724,25 +2769,25 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="G42" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="I42" t="s">
-        <v>93</v>
+        <v>256</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="25.05" customHeight="1">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -2759,25 +2804,25 @@
         <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G43" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="I43" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="25.05" customHeight="1">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -2794,25 +2839,25 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="G44" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="I44" t="s">
-        <v>98</v>
+        <v>245</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="25.05" customHeight="1">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -2829,38 +2874,42 @@
         <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="G45" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="H45" t="s">
-        <v>219</v>
-      </c>
-      <c r="I45" t="s">
-        <v>101</v>
+        <v>209</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I8" r:id="rId1" xr:uid="{1A4A2B9E-0CF0-4F32-B1E6-76CB1EA684D3}"/>
+    <hyperlink ref="I22" r:id="rId2" xr:uid="{34F5DABA-38DA-4010-99F9-4E94BC390DB5}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E214872-B259-4D60-A09C-B4FCA0969047}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
